--- a/docs/legal/gap-instruments/case-briefs/qa/cold-start/evidence-update-corrected.xlsx
+++ b/docs/legal/gap-instruments/case-briefs/qa/cold-start/evidence-update-corrected.xlsx
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>dde6c0ebd5e7d1d19757346feade554732bcb34ce35e90f8ab7e5101923021f9</t>
+          <t>a31397f46b49101ba75d632de23edbfc8eef3205c77571e41fe653be2fa8def5</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1f764afff496bd216dfca3fd1ffac4accf7433cf0404557f894312f82887577a</t>
+          <t>2cf05a38cb0a634ba8355e6f5e046977ada35dad0a83d210b7cd265491c59e20</t>
         </is>
       </c>
     </row>
